--- a/output/roomself_excel/2197.xlsx
+++ b/output/roomself_excel/2197.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113058</v>
+        <v>114273</v>
       </c>
       <c r="D2" t="n">
-        <v>2728</v>
+        <v>2748</v>
       </c>
       <c r="E2" t="n">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="F2" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>110880</v>
+        <v>220269</v>
       </c>
       <c r="D3" t="n">
-        <v>2704</v>
+        <v>3848</v>
       </c>
       <c r="E3" t="n">
-        <v>422</v>
+        <v>637</v>
       </c>
       <c r="F3" t="n">
-        <v>306</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>408884</v>
+        <v>113058</v>
       </c>
       <c r="D4" t="n">
-        <v>6972</v>
+        <v>2728</v>
       </c>
       <c r="E4" t="n">
-        <v>827</v>
+        <v>415</v>
       </c>
       <c r="F4" t="n">
-        <v>637</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42728</v>
+        <v>110880</v>
       </c>
       <c r="D5" t="n">
-        <v>2004</v>
+        <v>2704</v>
       </c>
       <c r="E5" t="n">
-        <v>121</v>
+        <v>422</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30459</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="n">
-        <v>1432</v>
+        <v>2116</v>
       </c>
       <c r="E6" t="n">
-        <v>183</v>
+        <v>307</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>71122</v>
+        <v>8643</v>
       </c>
       <c r="D7" t="n">
-        <v>2140</v>
+        <v>784</v>
       </c>
       <c r="E7" t="n">
-        <v>312</v>
+        <v>129</v>
       </c>
       <c r="F7" t="n">
-        <v>274</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>57895</v>
+        <v>74342</v>
       </c>
       <c r="D8" t="n">
-        <v>2116</v>
+        <v>2852</v>
       </c>
       <c r="E8" t="n">
-        <v>307</v>
+        <v>396</v>
       </c>
       <c r="F8" t="n">
-        <v>212</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23360</v>
+        <v>42728</v>
       </c>
       <c r="D9" t="n">
-        <v>1224</v>
+        <v>2004</v>
       </c>
       <c r="E9" t="n">
-        <v>186</v>
+        <v>121</v>
       </c>
       <c r="F9" t="n">
-        <v>172</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,64 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8643</v>
+        <v>30459</v>
       </c>
       <c r="D10" t="n">
-        <v>784</v>
+        <v>1432</v>
       </c>
       <c r="E10" t="n">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>71122</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2140</v>
+      </c>
+      <c r="E11" t="n">
+        <v>312</v>
+      </c>
+      <c r="F11" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>23360</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1224</v>
+      </c>
+      <c r="E12" t="n">
+        <v>186</v>
+      </c>
+      <c r="F12" t="n">
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/2197.xlsx
+++ b/output/roomself_excel/2197.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2748</v>
       </c>
-      <c r="E2" t="n">
-        <v>424</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>314</v>
+        <v>398</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>286</v>
+      </c>
+      <c r="J2" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3848</v>
       </c>
-      <c r="E3" t="n">
-        <v>637</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>403</v>
+        <v>573</v>
+      </c>
+      <c r="G3" t="n">
+        <v>26</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>751</v>
+      </c>
+      <c r="J3" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>2728</v>
       </c>
-      <c r="E4" t="n">
-        <v>415</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>312</v>
+        <v>285</v>
+      </c>
+      <c r="G4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>371</v>
+      </c>
+      <c r="J4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +609,27 @@
       <c r="D5" t="n">
         <v>2704</v>
       </c>
-      <c r="E5" t="n">
-        <v>422</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>306</v>
+        <v>280</v>
+      </c>
+      <c r="G5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>396</v>
+      </c>
+      <c r="J5" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -563,11 +647,27 @@
       <c r="D6" t="n">
         <v>2116</v>
       </c>
-      <c r="E6" t="n">
-        <v>307</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>200</v>
+        <v>174</v>
+      </c>
+      <c r="G6" t="n">
+        <v>26</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>281</v>
+      </c>
+      <c r="J6" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +685,20 @@
       <c r="D7" t="n">
         <v>784</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>129</v>
       </c>
-      <c r="F7" t="n">
-        <v>26</v>
-      </c>
+      <c r="G7" t="n">
+        <v>26</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +715,20 @@
       <c r="D8" t="n">
         <v>2852</v>
       </c>
-      <c r="E8" t="n">
-        <v>396</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>323</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="G8" t="n">
+        <v>26</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +745,20 @@
       <c r="D9" t="n">
         <v>2004</v>
       </c>
-      <c r="E9" t="n">
-        <v>121</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="G9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +775,20 @@
       <c r="D10" t="n">
         <v>1432</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>183</v>
       </c>
-      <c r="F10" t="n">
-        <v>26</v>
-      </c>
+      <c r="G10" t="n">
+        <v>26</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,11 +805,27 @@
       <c r="D11" t="n">
         <v>2140</v>
       </c>
-      <c r="E11" t="n">
-        <v>312</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>274</v>
+        <v>236</v>
+      </c>
+      <c r="G11" t="n">
+        <v>25</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>287</v>
+      </c>
+      <c r="J11" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -695,11 +843,27 @@
       <c r="D12" t="n">
         <v>1224</v>
       </c>
-      <c r="E12" t="n">
-        <v>186</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>172</v>
+        <v>160</v>
+      </c>
+      <c r="G12" t="n">
+        <v>26</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>146</v>
+      </c>
+      <c r="J12" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
